--- a/pregenereated_results/s2/ate_summary_survey.xlsx
+++ b/pregenereated_results/s2/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3982233096578141</v>
+        <v>0.3982233096578142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03926983810596111</v>
+        <v>0.03926983810596112</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3212558412914117</v>
+        <v>0.3212558412914118</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4751907780242164</v>
+        <v>0.4751907780242166</v>
       </c>
       <c r="G2" t="n">
-        <v>3.645104327879786e-24</v>
+        <v>3.645104327879733e-24</v>
       </c>
       <c r="H2" t="n">
         <v>0.4740212656916218</v>
@@ -557,10 +557,10 @@
         <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N2" t="n">
-        <v>1.093531298363936e-23</v>
+        <v>1.09353129836392e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04059280522771685</v>
+        <v>-0.0405928052277169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -594,13 +594,13 @@
         <v>0.04219295914182773</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1232894855468692</v>
+        <v>-0.1232894855468693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04210387509143552</v>
+        <v>0.04210387509143548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3360117637295977</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="H3" t="n">
         <v>-0.06073443341649937</v>
@@ -618,10 +618,10 @@
         <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3360117637295977</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04275687264023308</v>
+        <v>0.0427568726402331</v>
       </c>
       <c r="E4" t="n">
         <v>0.1462248547236112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3138287156564569</v>
+        <v>0.313828715656457</v>
       </c>
       <c r="G4" t="n">
-        <v>7.453607464503556e-08</v>
+        <v>7.453607464503609e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2684816016281898</v>
+        <v>0.2684816016281894</v>
       </c>
       <c r="I4" t="n">
-        <v>9.10917724022616</v>
+        <v>9.109177240226145</v>
       </c>
       <c r="J4" t="n">
         <v>3.052316367566833</v>
@@ -675,10 +675,10 @@
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N4" t="n">
-        <v>1.118041119675534e-07</v>
+        <v>1.118041119675541e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
